--- a/artfynd/A 6816-2025 artfynd.xlsx
+++ b/artfynd/A 6816-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123435133</v>
+        <v>123434920</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346779</v>
+        <v>346797</v>
       </c>
       <c r="R2" t="n">
-        <v>6438251</v>
+        <v>6438169</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillkråkehack i nedersta delen hos en högstubbe av tall.</t>
+          <t>Satt i mosseskogen och sjöng.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123434920</v>
+        <v>123435079</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>8430</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,37 +806,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346797</v>
+        <v>346745</v>
       </c>
       <c r="R3" t="n">
-        <v>6438169</v>
+        <v>6438250</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +883,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Satt i mosseskogen och sjöng.</t>
+          <t>Björksplintborrens rader av hål satt på en låga i mosseskogen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,6 +892,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123435079</v>
+        <v>123434846</v>
       </c>
       <c r="B4" t="n">
         <v>8430</v>
@@ -958,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346745</v>
+        <v>346803</v>
       </c>
       <c r="R4" t="n">
-        <v>6438250</v>
+        <v>6438047</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Björksplintborrens rader av hål satt på en låga i mosseskogen.</t>
+          <t>Björksplintborrens rader med hål satt på en björkhögstubbe i våtmarkskanten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123434846</v>
+        <v>123434907</v>
       </c>
       <c r="B5" t="n">
-        <v>8430</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,34 +1040,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1075,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346803</v>
+        <v>346764</v>
       </c>
       <c r="R5" t="n">
-        <v>6438047</v>
+        <v>6438165</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1116,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Björksplintborrens rader med hål satt på en björkhögstubbe i våtmarkskanten.</t>
+          <t>Spillkråkans hackspår efter födosök vid basen av ett torrträd av en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,7 +1125,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123434907</v>
+        <v>123435133</v>
       </c>
       <c r="B6" t="n">
         <v>57497</v>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346764</v>
+        <v>346779</v>
       </c>
       <c r="R6" t="n">
-        <v>6438165</v>
+        <v>6438251</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillkråkans hackspår efter födosök vid basen av ett torrträd av en gran.</t>
+          <t>Spillkråkehack i nedersta delen hos en högstubbe av tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 6816-2025 artfynd.xlsx
+++ b/artfynd/A 6816-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123435133</v>
+        <v>123434920</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346779</v>
+        <v>346797</v>
       </c>
       <c r="R2" t="n">
-        <v>6438251</v>
+        <v>6438169</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillkråkehack i nedersta delen hos en högstubbe av tall.</t>
+          <t>Satt i mosseskogen och sjöng.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +797,7 @@
         <v>123435079</v>
       </c>
       <c r="B3" t="n">
-        <v>8430</v>
+        <v>8434</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123434920</v>
+        <v>123434907</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>57503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,33 +927,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346797</v>
+        <v>346764</v>
       </c>
       <c r="R4" t="n">
-        <v>6438169</v>
+        <v>6438165</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Satt i mosseskogen och sjöng.</t>
+          <t>Spillkråkans hackspår efter födosök vid basen av ett torrträd av en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123434907</v>
+        <v>123435133</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346764</v>
+        <v>346779</v>
       </c>
       <c r="R5" t="n">
-        <v>6438165</v>
+        <v>6438251</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillkråkans hackspår efter födosök vid basen av ett torrträd av en gran.</t>
+          <t>Spillkråkehack i nedersta delen hos en högstubbe av tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,7 +1144,7 @@
         <v>123434846</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>8434</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 6816-2025 artfynd.xlsx
+++ b/artfynd/A 6816-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123434920</v>
       </c>
       <c r="B2" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123435079</v>
+        <v>123435133</v>
       </c>
       <c r="B3" t="n">
-        <v>8434</v>
+        <v>57506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,34 +806,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -843,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346745</v>
+        <v>346779</v>
       </c>
       <c r="R3" t="n">
-        <v>6438250</v>
+        <v>6438251</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Björksplintborrens rader av hål satt på en låga i mosseskogen.</t>
+          <t>Spillkråkehack i nedersta delen hos en högstubbe av tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +891,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -914,7 +912,7 @@
         <v>123434907</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123435133</v>
+        <v>123434846</v>
       </c>
       <c r="B5" t="n">
-        <v>57503</v>
+        <v>8436</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,33 +1036,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1074,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346779</v>
+        <v>346803</v>
       </c>
       <c r="R5" t="n">
-        <v>6438251</v>
+        <v>6438047</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1113,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillkråkehack i nedersta delen hos en högstubbe av tall.</t>
+          <t>Björksplintborrens rader med hål satt på en björkhögstubbe i våtmarkskanten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,6 +1122,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123434846</v>
+        <v>123435079</v>
       </c>
       <c r="B6" t="n">
-        <v>8434</v>
+        <v>8436</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346803</v>
+        <v>346745</v>
       </c>
       <c r="R6" t="n">
-        <v>6438047</v>
+        <v>6438250</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Björksplintborrens rader med hål satt på en björkhögstubbe i våtmarkskanten.</t>
+          <t>Björksplintborrens rader av hål satt på en låga i mosseskogen.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 6816-2025 artfynd.xlsx
+++ b/artfynd/A 6816-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123434920</v>
+        <v>123435079</v>
       </c>
       <c r="B2" t="n">
-        <v>57643</v>
+        <v>8436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346797</v>
+        <v>346745</v>
       </c>
       <c r="R2" t="n">
-        <v>6438169</v>
+        <v>6438250</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +764,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Satt i mosseskogen och sjöng.</t>
+          <t>Björksplintborrens rader av hål satt på en låga i mosseskogen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123435133</v>
+        <v>123434907</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346779</v>
+        <v>346764</v>
       </c>
       <c r="R3" t="n">
-        <v>6438251</v>
+        <v>6438165</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -882,7 +880,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spillkråkehack i nedersta delen hos en högstubbe av tall.</t>
+          <t>Spillkråkans hackspår efter födosök vid basen av ett torrträd av en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123434907</v>
+        <v>123435133</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346764</v>
+        <v>346779</v>
       </c>
       <c r="R4" t="n">
-        <v>6438165</v>
+        <v>6438251</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,7 +995,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillkråkans hackspår efter födosök vid basen av ett torrträd av en gran.</t>
+          <t>Spillkråkehack i nedersta delen hos en högstubbe av tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123434846</v>
+        <v>123434920</v>
       </c>
       <c r="B5" t="n">
-        <v>8436</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1034,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1073,13 +1074,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346803</v>
+        <v>346797</v>
       </c>
       <c r="R5" t="n">
-        <v>6438047</v>
+        <v>6438169</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1114,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Björksplintborrens rader med hål satt på en björkhögstubbe i våtmarkskanten.</t>
+          <t>Satt i mosseskogen och sjöng.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1123,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123435079</v>
+        <v>123434846</v>
       </c>
       <c r="B6" t="n">
         <v>8436</v>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346745</v>
+        <v>346803</v>
       </c>
       <c r="R6" t="n">
-        <v>6438250</v>
+        <v>6438047</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Björksplintborrens rader av hål satt på en låga i mosseskogen.</t>
+          <t>Björksplintborrens rader med hål satt på en björkhögstubbe i våtmarkskanten.</t>
         </is>
       </c>
       <c r="AD6" t="b">
